--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61126685</v>
+        <v>136778080</v>
       </c>
       <c r="B3" t="n">
-        <v>93191</v>
+        <v>93401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,37 +818,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752731</v>
+        <v>752791</v>
       </c>
       <c r="R3" t="n">
-        <v>7094719</v>
+        <v>7094776</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,12 +872,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-08-24</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-08-24</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,65 +902,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61126685</t>
+          <t>https://artportalen.se/Sighting/136778080</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128787956</v>
+        <v>61126685</v>
       </c>
       <c r="B4" t="n">
-        <v>93201</v>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752794</v>
+        <v>752731</v>
       </c>
       <c r="R4" t="n">
-        <v>7094637</v>
+        <v>7094719</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,17 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2016-08-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Under silverved just bredvid parkeringen</t>
+          <t>2016-08-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,24 +1004,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787956</t>
+          <t>https://artportalen.se/Sighting/61126685</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128787957</v>
+        <v>128787956</v>
       </c>
       <c r="B5" t="n">
         <v>93201</v>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752711</v>
+        <v>752794</v>
       </c>
       <c r="R5" t="n">
-        <v>7094778</v>
+        <v>7094637</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Under silverved just bredvid parkeringen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,13 +1122,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787957</t>
+          <t>https://artportalen.se/Sighting/128787956</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128787959</v>
+        <v>128787957</v>
       </c>
       <c r="B6" t="n">
         <v>93201</v>
@@ -1158,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752779</v>
+        <v>752711</v>
       </c>
       <c r="R6" t="n">
-        <v>7094692</v>
+        <v>7094778</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>under silverlåga, delvis nedbruten, halvvägs i mossa</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,13 +1229,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787959</t>
+          <t>https://artportalen.se/Sighting/128787957</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128787961</v>
+        <v>128787959</v>
       </c>
       <c r="B7" t="n">
         <v>93201</v>
@@ -1265,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752808</v>
+        <v>752779</v>
       </c>
       <c r="R7" t="n">
-        <v>7094672</v>
+        <v>7094692</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,7 +1310,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Under kortare silverlåga, ganska nära lång silverlåga som har smalfotad taggsvamp också</t>
+          <t>under silverlåga, delvis nedbruten, halvvägs i mossa</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,13 +1336,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787961</t>
+          <t>https://artportalen.se/Sighting/128787959</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128787964</v>
+        <v>128787961</v>
       </c>
       <c r="B8" t="n">
         <v>93201</v>
@@ -1372,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752791</v>
+        <v>752808</v>
       </c>
       <c r="R8" t="n">
-        <v>7094671</v>
+        <v>7094672</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1412,7 +1417,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Under tunn tallåga nedsänkt i mossa</t>
+          <t>Under kortare silverlåga, ganska nära lång silverlåga som har smalfotad taggsvamp också</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,13 +1443,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787964</t>
+          <t>https://artportalen.se/Sighting/128787961</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128787966</v>
+        <v>128787964</v>
       </c>
       <c r="B9" t="n">
         <v>93201</v>
@@ -1479,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752758</v>
+        <v>752791</v>
       </c>
       <c r="R9" t="n">
-        <v>7094712</v>
+        <v>7094671</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1519,7 +1524,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
+          <t>Under tunn tallåga nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,13 +1550,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787966</t>
+          <t>https://artportalen.se/Sighting/128787964</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128787967</v>
+        <v>128787966</v>
       </c>
       <c r="B10" t="n">
         <v>93201</v>
@@ -1586,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752787</v>
+        <v>752758</v>
       </c>
       <c r="R10" t="n">
-        <v>7094681</v>
+        <v>7094712</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1626,7 +1631,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Tallåga nästan helt nedsänkt i mossa</t>
+          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,13 +1657,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787967</t>
+          <t>https://artportalen.se/Sighting/128787966</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128787969</v>
+        <v>128787967</v>
       </c>
       <c r="B11" t="n">
         <v>93201</v>
@@ -1693,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>752776</v>
+        <v>752787</v>
       </c>
       <c r="R11" t="n">
-        <v>7094659</v>
+        <v>7094681</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1733,7 +1738,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Talllåga kort, vid grusväg</t>
+          <t>Tallåga nästan helt nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,13 +1764,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787969</t>
+          <t>https://artportalen.se/Sighting/128787967</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128787971</v>
+        <v>128787969</v>
       </c>
       <c r="B12" t="n">
         <v>93201</v>
@@ -1800,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752800</v>
+        <v>752776</v>
       </c>
       <c r="R12" t="n">
-        <v>7094653</v>
+        <v>7094659</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1840,7 +1845,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under tallåga</t>
+          <t>Talllåga kort, vid grusväg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,13 +1871,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787971</t>
+          <t>https://artportalen.se/Sighting/128787969</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128787972</v>
+        <v>128787971</v>
       </c>
       <c r="B13" t="n">
         <v>93201</v>
@@ -1907,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752808</v>
+        <v>752800</v>
       </c>
       <c r="R13" t="n">
-        <v>7094654</v>
+        <v>7094653</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,7 +1952,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Under silverlåga mellan stigar</t>
+          <t>Under tallåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,13 +1978,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787972</t>
+          <t>https://artportalen.se/Sighting/128787971</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128787973</v>
+        <v>128787972</v>
       </c>
       <c r="B14" t="n">
         <v>93201</v>
@@ -2014,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>752821</v>
+        <v>752808</v>
       </c>
       <c r="R14" t="n">
-        <v>7094673</v>
+        <v>7094654</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2054,7 +2059,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Under silverlåga mellan stigar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,13 +2085,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787973</t>
+          <t>https://artportalen.se/Sighting/128787972</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128815357</v>
+        <v>128787973</v>
       </c>
       <c r="B15" t="n">
         <v>93201</v>
@@ -2121,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752752</v>
+        <v>752821</v>
       </c>
       <c r="R15" t="n">
-        <v>7094775</v>
+        <v>7094673</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2151,17 +2156,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Silverlåga 2delad norra delen</t>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,13 +2192,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815357</t>
+          <t>https://artportalen.se/Sighting/128787973</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128815360</v>
+        <v>128815357</v>
       </c>
       <c r="B16" t="n">
         <v>93201</v>
@@ -2228,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752738</v>
+        <v>752752</v>
       </c>
       <c r="R16" t="n">
-        <v>7094815</v>
+        <v>7094775</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2268,7 +2273,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>tunn tallgren nedsänkt i mossa</t>
+          <t>Silverlåga 2delad norra delen</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,13 +2299,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815360</t>
+          <t>https://artportalen.se/Sighting/128815357</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128815361</v>
+        <v>128815360</v>
       </c>
       <c r="B17" t="n">
         <v>93201</v>
@@ -2335,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>752840</v>
+        <v>752738</v>
       </c>
       <c r="R17" t="n">
-        <v>7094744</v>
+        <v>7094815</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2375,7 +2380,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>silverlåga rotvälta</t>
+          <t>tunn tallgren nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,13 +2406,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815361</t>
+          <t>https://artportalen.se/Sighting/128815360</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128815362</v>
+        <v>128815361</v>
       </c>
       <c r="B18" t="n">
         <v>93201</v>
@@ -2442,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>752811</v>
+        <v>752840</v>
       </c>
       <c r="R18" t="n">
-        <v>7094687</v>
+        <v>7094744</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2482,7 +2487,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>silverlåga nedbruten delvis</t>
+          <t>silverlåga rotvälta</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,54 +2513,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815362</t>
+          <t>https://artportalen.se/Sighting/128815361</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>61126684</v>
+        <v>128815362</v>
       </c>
       <c r="B19" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>752685</v>
+        <v>752811</v>
       </c>
       <c r="R19" t="n">
-        <v>7094814</v>
+        <v>7094687</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2579,12 +2584,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2016-08-24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2016-08-24</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>silverlåga nedbruten delvis</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,27 +2609,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61126684</t>
+          <t>https://artportalen.se/Sighting/128815362</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128815356</v>
+        <v>61126684</v>
       </c>
       <c r="B20" t="n">
-        <v>93223</v>
+        <v>93209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2627,40 +2637,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5448</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752793</v>
+        <v>752685</v>
       </c>
       <c r="R20" t="n">
-        <v>7094748</v>
+        <v>7094814</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2684,17 +2691,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2016-08-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat. Kollekt202509005 Artbestämd av Sten Svantesson 20251227</t>
+          <t>2016-08-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,85 +2705,55 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Silverved</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Silverved</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>Sten Svantesson</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815356</t>
+          <t>https://artportalen.se/Sighting/61126684</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128815359</v>
+        <v>128815356</v>
       </c>
       <c r="B21" t="n">
-        <v>93181</v>
+        <v>93223</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6055</v>
+        <v>5448</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2794,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752797</v>
+        <v>752793</v>
       </c>
       <c r="R21" t="n">
-        <v>7094712</v>
+        <v>7094748</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2834,7 +2806,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Silverlåga, delvis nedbruten. Även tajgataggsvamp under samma låga.</t>
+          <t>Kollekt insamlat. Kollekt202509005 Artbestämd av Sten Svantesson 20251227</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2847,7 +2819,36 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AT21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Silverved</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Silverved</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="AW21" t="inlineStr">
         <is>
           <t>Roger Olofsson</t>
@@ -2861,16 +2862,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815359</t>
+          <t>https://artportalen.se/Sighting/128815356</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128787940</v>
+        <v>128815359</v>
       </c>
       <c r="B22" t="n">
-        <v>90710</v>
+        <v>93181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2878,38 +2879,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6286</v>
+        <v>6055</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752757</v>
+        <v>752797</v>
       </c>
       <c r="R22" t="n">
-        <v>7094726</v>
+        <v>7094712</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2936,17 +2936,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Växte mellan 2 äldre silverlågor</t>
+          <t>Silverlåga, delvis nedbruten. Även tajgataggsvamp under samma låga.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,6 +2955,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2972,16 +2973,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787940</t>
+          <t>https://artportalen.se/Sighting/128815359</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128787943</v>
+        <v>136778073</v>
       </c>
       <c r="B23" t="n">
-        <v>90710</v>
+        <v>90874</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2989,38 +2990,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>752782</v>
+        <v>752781</v>
       </c>
       <c r="R23" t="n">
-        <v>7094651</v>
+        <v>7094820</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3047,17 +3044,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Nära tallstam</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3072,27 +3074,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787943</t>
+          <t>https://artportalen.se/Sighting/136778073</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128787944</v>
+        <v>136778077</v>
       </c>
       <c r="B24" t="n">
-        <v>90710</v>
+        <v>90874</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3100,38 +3102,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>752769</v>
+        <v>752764</v>
       </c>
       <c r="R24" t="n">
-        <v>7094680</v>
+        <v>7094829</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3158,12 +3156,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3178,74 +3186,66 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787944</t>
+          <t>https://artportalen.se/Sighting/136778077</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128787945</v>
+        <v>128787940</v>
       </c>
       <c r="B25" t="n">
-        <v>58114</v>
+        <v>90710</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>752784</v>
+        <v>752757</v>
       </c>
       <c r="R25" t="n">
-        <v>7094657</v>
+        <v>7094726</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3275,19 +3275,14 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:45</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växte mellan 2 äldre silverlågor</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3313,44 +3308,43 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787945</t>
+          <t>https://artportalen.se/Sighting/128787940</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128815352</v>
+        <v>128787943</v>
       </c>
       <c r="B26" t="n">
-        <v>58114</v>
+        <v>90710</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3359,10 +3353,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752743</v>
+        <v>752782</v>
       </c>
       <c r="R26" t="n">
-        <v>7094781</v>
+        <v>7094651</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3389,12 +3383,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Nära tallstam</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3420,59 +3419,55 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815352</t>
+          <t>https://artportalen.se/Sighting/128787943</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128815353</v>
+        <v>128787944</v>
       </c>
       <c r="B27" t="n">
-        <v>58114</v>
+        <v>90710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>752794</v>
+        <v>752769</v>
       </c>
       <c r="R27" t="n">
-        <v>7094682</v>
+        <v>7094680</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3499,12 +3494,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3530,47 +3525,50 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815353</t>
+          <t>https://artportalen.se/Sighting/128787944</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128787974</v>
+        <v>128787945</v>
       </c>
       <c r="B28" t="n">
-        <v>56884</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>208255</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3580,10 +3578,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>752825</v>
+        <v>752784</v>
       </c>
       <c r="R28" t="n">
-        <v>7094640</v>
+        <v>7094657</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3615,7 +3613,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3625,12 +3623,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Vilar på silverlåga</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3639,7 +3632,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3657,51 +3649,56 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787974</t>
+          <t>https://artportalen.se/Sighting/128787945</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128787946</v>
+        <v>128815352</v>
       </c>
       <c r="B29" t="n">
-        <v>93228</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>232140</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752779</v>
+        <v>752743</v>
       </c>
       <c r="R29" t="n">
-        <v>7094659</v>
+        <v>7094781</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3728,17 +3725,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Under silverved, grövre tallgren</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3764,43 +3756,48 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787946</t>
+          <t>https://artportalen.se/Sighting/128815352</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128815354</v>
+        <v>128815353</v>
       </c>
       <c r="B30" t="n">
-        <v>93228</v>
+        <v>58114</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>232140</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3808,10 +3805,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>752754</v>
+        <v>752794</v>
       </c>
       <c r="R30" t="n">
-        <v>7094754</v>
+        <v>7094682</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3846,31 +3843,16 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Under silverlåga. Kollekt insamlat kollekt202509004 Artbestämd av Sten Svantesson 20251227</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AS30" t="inlineStr">
-        <is>
-          <t>Sten Svantesson</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
           <t>Roger Olofsson</t>
@@ -3884,43 +3866,49 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815354</t>
+          <t>https://artportalen.se/Sighting/128815353</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128815358</v>
+        <v>128787974</v>
       </c>
       <c r="B31" t="n">
-        <v>93228</v>
+        <v>56884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>232140</v>
+        <v>208255</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3928,10 +3916,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>752797</v>
+        <v>752825</v>
       </c>
       <c r="R31" t="n">
-        <v>7094712</v>
+        <v>7094640</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3958,17 +3946,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Silverlåga, delvis nedbruten. Kollekt insamlat. Kollekt202509006 Även spadskinn under samma låga Artbestämd av Sten Svantesson 20251227</t>
+          <t>Vilar på silverlåga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3981,16 +3979,7 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>Sten Svantesson</t>
-        </is>
-      </c>
-      <c r="AT31" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
           <t>Roger Olofsson</t>
@@ -4003,6 +3992,353 @@
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787974</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128787946</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>752779</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7094659</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Under silverved, grövre tallgren</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787946</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128815354</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>752754</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7094754</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Under silverlåga. Kollekt insamlat kollekt202509004 Artbestämd av Sten Svantesson 20251227</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128815354</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128815358</v>
+      </c>
+      <c r="B34" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>752797</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7094712</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Silverlåga, delvis nedbruten. Kollekt insamlat. Kollekt202509006 Även spadskinn under samma låga Artbestämd av Sten Svantesson 20251227</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128815358</t>
         </is>
@@ -4040,6 +4376,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,32 +807,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136778080</v>
+        <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93401</v>
+        <v>93425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752791</v>
+        <v>752772</v>
       </c>
       <c r="R3" t="n">
-        <v>7094776</v>
+        <v>7094821</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +872,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,22 +907,22 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alice Thomander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136778080</t>
+          <t>https://artportalen.se/Sighting/136812533</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61126685</v>
+        <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93191</v>
+        <v>93401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,37 +930,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752731</v>
+        <v>752791</v>
       </c>
       <c r="R4" t="n">
-        <v>7094719</v>
+        <v>7094776</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,12 +984,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-08-24</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-08-24</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,65 +1014,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61126685</t>
+          <t>https://artportalen.se/Sighting/136778080</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128787956</v>
+        <v>61126685</v>
       </c>
       <c r="B5" t="n">
-        <v>93201</v>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752794</v>
+        <v>752731</v>
       </c>
       <c r="R5" t="n">
-        <v>7094637</v>
+        <v>7094719</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,17 +1096,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2016-08-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Under silverved just bredvid parkeringen</t>
+          <t>2016-08-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,24 +1116,24 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787956</t>
+          <t>https://artportalen.se/Sighting/61126685</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128787957</v>
+        <v>128787956</v>
       </c>
       <c r="B6" t="n">
         <v>93201</v>
@@ -1163,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752711</v>
+        <v>752794</v>
       </c>
       <c r="R6" t="n">
-        <v>7094778</v>
+        <v>7094637</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Under silverved i hög, grenar</t>
+          <t>Under silverved just bredvid parkeringen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,13 +1234,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787957</t>
+          <t>https://artportalen.se/Sighting/128787956</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128787959</v>
+        <v>128787957</v>
       </c>
       <c r="B7" t="n">
         <v>93201</v>
@@ -1270,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752779</v>
+        <v>752711</v>
       </c>
       <c r="R7" t="n">
-        <v>7094692</v>
+        <v>7094778</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>under silverlåga, delvis nedbruten, halvvägs i mossa</t>
+          <t>Under silverved i hög, grenar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,13 +1341,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787959</t>
+          <t>https://artportalen.se/Sighting/128787957</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128787961</v>
+        <v>128787959</v>
       </c>
       <c r="B8" t="n">
         <v>93201</v>
@@ -1377,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752808</v>
+        <v>752779</v>
       </c>
       <c r="R8" t="n">
-        <v>7094672</v>
+        <v>7094692</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,7 +1422,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Under kortare silverlåga, ganska nära lång silverlåga som har smalfotad taggsvamp också</t>
+          <t>under silverlåga, delvis nedbruten, halvvägs i mossa</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,13 +1448,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787961</t>
+          <t>https://artportalen.se/Sighting/128787959</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128787964</v>
+        <v>128787961</v>
       </c>
       <c r="B9" t="n">
         <v>93201</v>
@@ -1484,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752791</v>
+        <v>752808</v>
       </c>
       <c r="R9" t="n">
-        <v>7094671</v>
+        <v>7094672</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1524,7 +1529,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Under tunn tallåga nedsänkt i mossa</t>
+          <t>Under kortare silverlåga, ganska nära lång silverlåga som har smalfotad taggsvamp också</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,13 +1555,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787964</t>
+          <t>https://artportalen.se/Sighting/128787961</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128787966</v>
+        <v>128787964</v>
       </c>
       <c r="B10" t="n">
         <v>93201</v>
@@ -1591,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752758</v>
+        <v>752791</v>
       </c>
       <c r="R10" t="n">
-        <v>7094712</v>
+        <v>7094671</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1631,7 +1636,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
+          <t>Under tunn tallåga nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,13 +1662,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787966</t>
+          <t>https://artportalen.se/Sighting/128787964</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128787967</v>
+        <v>128787966</v>
       </c>
       <c r="B11" t="n">
         <v>93201</v>
@@ -1698,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>752787</v>
+        <v>752758</v>
       </c>
       <c r="R11" t="n">
-        <v>7094681</v>
+        <v>7094712</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1738,7 +1743,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Tallåga nästan helt nedsänkt i mossa</t>
+          <t>Under talllåga, spets mot stående tall. Finns fk under fler silvervedbitar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,13 +1769,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787967</t>
+          <t>https://artportalen.se/Sighting/128787966</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128787969</v>
+        <v>128787967</v>
       </c>
       <c r="B12" t="n">
         <v>93201</v>
@@ -1805,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752776</v>
+        <v>752787</v>
       </c>
       <c r="R12" t="n">
-        <v>7094659</v>
+        <v>7094681</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1845,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Talllåga kort, vid grusväg</t>
+          <t>Tallåga nästan helt nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,13 +1876,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787969</t>
+          <t>https://artportalen.se/Sighting/128787967</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128787971</v>
+        <v>128787969</v>
       </c>
       <c r="B13" t="n">
         <v>93201</v>
@@ -1912,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752800</v>
+        <v>752776</v>
       </c>
       <c r="R13" t="n">
-        <v>7094653</v>
+        <v>7094659</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1952,7 +1957,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Under tallåga</t>
+          <t>Talllåga kort, vid grusväg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1978,13 +1983,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787971</t>
+          <t>https://artportalen.se/Sighting/128787969</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128787972</v>
+        <v>128787971</v>
       </c>
       <c r="B14" t="n">
         <v>93201</v>
@@ -2019,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>752808</v>
+        <v>752800</v>
       </c>
       <c r="R14" t="n">
-        <v>7094654</v>
+        <v>7094653</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2059,7 +2064,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Under silverlåga mellan stigar</t>
+          <t>Under tallåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2085,13 +2090,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787972</t>
+          <t>https://artportalen.se/Sighting/128787971</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128787973</v>
+        <v>128787972</v>
       </c>
       <c r="B15" t="n">
         <v>93201</v>
@@ -2126,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752821</v>
+        <v>752808</v>
       </c>
       <c r="R15" t="n">
-        <v>7094673</v>
+        <v>7094654</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2166,7 +2171,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Under silverlåga mellan stigar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,13 +2197,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787973</t>
+          <t>https://artportalen.se/Sighting/128787972</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128815357</v>
+        <v>128787973</v>
       </c>
       <c r="B16" t="n">
         <v>93201</v>
@@ -2233,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752752</v>
+        <v>752821</v>
       </c>
       <c r="R16" t="n">
-        <v>7094775</v>
+        <v>7094673</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2263,17 +2268,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Silverlåga 2delad norra delen</t>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2299,13 +2304,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815357</t>
+          <t>https://artportalen.se/Sighting/128787973</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128815360</v>
+        <v>128815357</v>
       </c>
       <c r="B17" t="n">
         <v>93201</v>
@@ -2340,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>752738</v>
+        <v>752752</v>
       </c>
       <c r="R17" t="n">
-        <v>7094815</v>
+        <v>7094775</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2380,7 +2385,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>tunn tallgren nedsänkt i mossa</t>
+          <t>Silverlåga 2delad norra delen</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,13 +2411,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815360</t>
+          <t>https://artportalen.se/Sighting/128815357</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128815361</v>
+        <v>128815360</v>
       </c>
       <c r="B18" t="n">
         <v>93201</v>
@@ -2447,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>752840</v>
+        <v>752738</v>
       </c>
       <c r="R18" t="n">
-        <v>7094744</v>
+        <v>7094815</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2487,7 +2492,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>silverlåga rotvälta</t>
+          <t>tunn tallgren nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,13 +2518,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815361</t>
+          <t>https://artportalen.se/Sighting/128815360</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128815362</v>
+        <v>128815361</v>
       </c>
       <c r="B19" t="n">
         <v>93201</v>
@@ -2554,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>752811</v>
+        <v>752840</v>
       </c>
       <c r="R19" t="n">
-        <v>7094687</v>
+        <v>7094744</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2594,7 +2599,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>silverlåga nedbruten delvis</t>
+          <t>silverlåga rotvälta</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2620,54 +2625,54 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815362</t>
+          <t>https://artportalen.se/Sighting/128815361</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>61126684</v>
+        <v>128815362</v>
       </c>
       <c r="B20" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752685</v>
+        <v>752811</v>
       </c>
       <c r="R20" t="n">
-        <v>7094814</v>
+        <v>7094687</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2691,12 +2696,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2016-08-24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2016-08-24</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>silverlåga nedbruten delvis</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,27 +2721,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61126684</t>
+          <t>https://artportalen.se/Sighting/128815362</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128815356</v>
+        <v>61126684</v>
       </c>
       <c r="B21" t="n">
-        <v>93223</v>
+        <v>93209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,40 +2749,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5448</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752793</v>
+        <v>752685</v>
       </c>
       <c r="R21" t="n">
-        <v>7094748</v>
+        <v>7094814</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2796,17 +2803,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2016-08-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat. Kollekt202509005 Artbestämd av Sten Svantesson 20251227</t>
+          <t>2016-08-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,85 +2817,55 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Silverved</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Silverved</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>Sten Svantesson</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815356</t>
+          <t>https://artportalen.se/Sighting/61126684</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128815359</v>
+        <v>128815356</v>
       </c>
       <c r="B22" t="n">
-        <v>93181</v>
+        <v>93223</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6055</v>
+        <v>5448</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2906,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752797</v>
+        <v>752793</v>
       </c>
       <c r="R22" t="n">
-        <v>7094712</v>
+        <v>7094748</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2946,7 +2918,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Silverlåga, delvis nedbruten. Även tajgataggsvamp under samma låga.</t>
+          <t>Kollekt insamlat. Kollekt202509005 Artbestämd av Sten Svantesson 20251227</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2959,7 +2931,36 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AT22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Silverved</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Silverved</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="AW22" t="inlineStr">
         <is>
           <t>Roger Olofsson</t>
@@ -2973,16 +2974,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815359</t>
+          <t>https://artportalen.se/Sighting/128815356</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136778073</v>
+        <v>128815359</v>
       </c>
       <c r="B23" t="n">
-        <v>90874</v>
+        <v>93181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2990,34 +2991,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6276</v>
+        <v>6055</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>752781</v>
+        <v>752797</v>
       </c>
       <c r="R23" t="n">
-        <v>7094820</v>
+        <v>7094712</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3044,22 +3048,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Silverlåga, delvis nedbruten. Även tajgataggsvamp under samma låga.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3068,30 +3067,31 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136778073</t>
+          <t>https://artportalen.se/Sighting/128815359</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136778077</v>
+        <v>136778073</v>
       </c>
       <c r="B24" t="n">
         <v>90874</v>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>752764</v>
+        <v>752781</v>
       </c>
       <c r="R24" t="n">
-        <v>7094829</v>
+        <v>7094820</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,16 +3197,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136778077</t>
+          <t>https://artportalen.se/Sighting/136778073</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128787940</v>
+        <v>136778077</v>
       </c>
       <c r="B25" t="n">
-        <v>90710</v>
+        <v>90874</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,38 +3214,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>752757</v>
+        <v>752764</v>
       </c>
       <c r="R25" t="n">
-        <v>7094726</v>
+        <v>7094829</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3272,17 +3268,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växte mellan 2 äldre silverlågor</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3297,24 +3298,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787940</t>
+          <t>https://artportalen.se/Sighting/136778077</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128787943</v>
+        <v>128787940</v>
       </c>
       <c r="B26" t="n">
         <v>90710</v>
@@ -3344,7 +3345,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3353,10 +3354,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752782</v>
+        <v>752757</v>
       </c>
       <c r="R26" t="n">
-        <v>7094651</v>
+        <v>7094726</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3393,7 +3394,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Nära tallstam</t>
+          <t>Växte mellan 2 äldre silverlågor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3419,13 +3420,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787943</t>
+          <t>https://artportalen.se/Sighting/128787940</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128787944</v>
+        <v>128787943</v>
       </c>
       <c r="B27" t="n">
         <v>90710</v>
@@ -3464,10 +3465,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>752769</v>
+        <v>752782</v>
       </c>
       <c r="R27" t="n">
-        <v>7094680</v>
+        <v>7094651</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3502,6 +3503,11 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Nära tallstam</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3525,63 +3531,55 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787944</t>
+          <t>https://artportalen.se/Sighting/128787943</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128787945</v>
+        <v>128787944</v>
       </c>
       <c r="B28" t="n">
-        <v>58114</v>
+        <v>90710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>752784</v>
+        <v>752769</v>
       </c>
       <c r="R28" t="n">
-        <v>7094657</v>
+        <v>7094680</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3611,19 +3609,9 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,56 +3637,51 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787945</t>
+          <t>https://artportalen.se/Sighting/128787944</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128815352</v>
+        <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>58114</v>
+        <v>90893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752743</v>
+        <v>752758</v>
       </c>
       <c r="R29" t="n">
-        <v>7094781</v>
+        <v>7094835</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3725,12 +3708,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3745,24 +3738,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson, Alice Thomander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815352</t>
+          <t>https://artportalen.se/Sighting/136812534</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128815353</v>
+        <v>128787945</v>
       </c>
       <c r="B30" t="n">
         <v>58114</v>
@@ -3790,7 +3783,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
@@ -3805,10 +3802,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>752794</v>
+        <v>752784</v>
       </c>
       <c r="R30" t="n">
-        <v>7094682</v>
+        <v>7094657</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3835,12 +3832,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3866,60 +3873,56 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815353</t>
+          <t>https://artportalen.se/Sighting/128787945</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128787974</v>
+        <v>128815352</v>
       </c>
       <c r="B31" t="n">
-        <v>56884</v>
+        <v>58114</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>208255</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>752825</v>
+        <v>752743</v>
       </c>
       <c r="R31" t="n">
-        <v>7094640</v>
+        <v>7094781</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3946,27 +3949,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Vilar på silverlåga</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3975,7 +3963,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3993,51 +3980,59 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787974</t>
+          <t>https://artportalen.se/Sighting/128815352</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128787946</v>
+        <v>128815353</v>
       </c>
       <c r="B32" t="n">
-        <v>93228</v>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>232140</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>752779</v>
+        <v>752794</v>
       </c>
       <c r="R32" t="n">
-        <v>7094659</v>
+        <v>7094682</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4064,17 +4059,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Under silverved, grövre tallgren</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4100,43 +4090,49 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787946</t>
+          <t>https://artportalen.se/Sighting/128815353</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128815354</v>
+        <v>128787974</v>
       </c>
       <c r="B33" t="n">
-        <v>93228</v>
+        <v>56884</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>232140</v>
+        <v>208255</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4144,10 +4140,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>752754</v>
+        <v>752825</v>
       </c>
       <c r="R33" t="n">
-        <v>7094754</v>
+        <v>7094640</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4174,17 +4170,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Under silverlåga. Kollekt insamlat kollekt202509004 Artbestämd av Sten Svantesson 20251227</t>
+          <t>Vilar på silverlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4197,16 +4203,7 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>Sten Svantesson</t>
-        </is>
-      </c>
-      <c r="AT33" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
           <t>Roger Olofsson</t>
@@ -4220,13 +4217,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128815354</t>
+          <t>https://artportalen.se/Sighting/128787974</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128815358</v>
+        <v>128787946</v>
       </c>
       <c r="B34" t="n">
         <v>93228</v>
@@ -4255,19 +4252,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>752797</v>
+        <v>752779</v>
       </c>
       <c r="R34" t="n">
-        <v>7094712</v>
+        <v>7094659</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4294,17 +4288,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Silverlåga, delvis nedbruten. Kollekt insamlat. Kollekt202509006 Även spadskinn under samma låga Artbestämd av Sten Svantesson 20251227</t>
+          <t>Under silverved, grövre tallgren</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4313,20 +4307,10 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>Sten Svantesson</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
           <t>Roger Olofsson</t>
@@ -4339,6 +4323,246 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787946</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128815354</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>752754</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7094754</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Under silverlåga. Kollekt insamlat kollekt202509004 Artbestämd av Sten Svantesson 20251227</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128815354</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128815358</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>752797</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7094712</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Silverlåga, delvis nedbruten. Kollekt insamlat. Kollekt202509006 Även spadskinn under samma låga Artbestämd av Sten Svantesson 20251227</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128815358</t>
         </is>
@@ -4379,6 +4603,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>136778073</v>
       </c>
       <c r="B24" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>136778077</v>
       </c>
       <c r="B25" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90893</v>
+        <v>90895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>136778073</v>
       </c>
       <c r="B24" t="n">
-        <v>90876</v>
+        <v>90878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>136778077</v>
       </c>
       <c r="B25" t="n">
-        <v>90876</v>
+        <v>90878</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>136778073</v>
       </c>
       <c r="B24" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>136778077</v>
       </c>
       <c r="B25" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>136778073</v>
       </c>
       <c r="B24" t="n">
-        <v>90880</v>
+        <v>90881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>136778077</v>
       </c>
       <c r="B25" t="n">
-        <v>90880</v>
+        <v>90881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>136778073</v>
       </c>
       <c r="B24" t="n">
-        <v>90881</v>
+        <v>90887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>136778077</v>
       </c>
       <c r="B25" t="n">
-        <v>90881</v>
+        <v>90887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>136778073</v>
       </c>
       <c r="B24" t="n">
-        <v>90887</v>
+        <v>90891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>136778077</v>
       </c>
       <c r="B25" t="n">
-        <v>90887</v>
+        <v>90891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>136778073</v>
       </c>
       <c r="B24" t="n">
-        <v>90891</v>
+        <v>90893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>136778077</v>
       </c>
       <c r="B25" t="n">
-        <v>90891</v>
+        <v>90893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>136778073</v>
       </c>
       <c r="B24" t="n">
-        <v>90893</v>
+        <v>90906</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>136778077</v>
       </c>
       <c r="B25" t="n">
-        <v>90893</v>
+        <v>90906</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>136778073</v>
       </c>
       <c r="B24" t="n">
-        <v>90906</v>
+        <v>90908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>136778077</v>
       </c>
       <c r="B25" t="n">
-        <v>90906</v>
+        <v>90908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>136778073</v>
       </c>
       <c r="B24" t="n">
-        <v>90908</v>
+        <v>90911</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>136778077</v>
       </c>
       <c r="B25" t="n">
-        <v>90908</v>
+        <v>90911</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>136778073</v>
       </c>
       <c r="B24" t="n">
-        <v>90911</v>
+        <v>90921</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>136778077</v>
       </c>
       <c r="B25" t="n">
-        <v>90911</v>
+        <v>90921</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>136778073</v>
       </c>
       <c r="B24" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>136778077</v>
       </c>
       <c r="B25" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>136778073</v>
       </c>
       <c r="B24" t="n">
-        <v>90922</v>
+        <v>90925</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>136778077</v>
       </c>
       <c r="B25" t="n">
-        <v>90922</v>
+        <v>90925</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136778080</v>
       </c>
       <c r="B4" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45657-2024 artfynd.xlsx
+++ b/artfynd/A 45657-2024 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136812533</v>
       </c>
       <c r="B3" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>136812534</v>
       </c>
       <c r="B29" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
